--- a/资产分组导入模板.example.xlsx
+++ b/资产分组导入模板.example.xlsx
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>https://172.21.193.214:53443</t>
+          <t>https://&lt;host&gt;:&lt;port&gt;</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1905,8 +1905,10 @@
           <t>dry_run</t>
         </is>
       </c>
-      <c r="B13" s="35" t="b">
-        <v>1</v>
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
@@ -2011,8 +2013,10 @@
           <t>batch_size</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>1</v>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
@@ -4069,141 +4073,54 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="8" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>阶段</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>动作</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>来源表</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>来源行号</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>对象</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>目标分组路径</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>信息</t>
-        </is>
-      </c>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr"/>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>plan</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>create_group</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>分组树</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr"/>
-      <c r="G7" s="10" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr"/>
-      <c r="I7" s="10" t="inlineStr"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>plan</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>move_terminal</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>终端清单</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr"/>
-      <c r="G8" s="10" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr"/>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr"/>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>create_group</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr"/>
-      <c r="I9" s="10" t="inlineStr"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
     </row>
     <row r="10" ht="27" customHeight="1" s="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>规划时间</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:23:48</t>
-        </is>
-      </c>
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
@@ -4213,68 +4130,28 @@
       <c r="I10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>启用终端</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>974</v>
-      </c>
+      <c r="A11" s="0" t="n"/>
+      <c r="B11" s="0" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>科室映射</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>46</v>
-      </c>
+      <c r="A12" s="0" t="n"/>
+      <c r="B12" s="0" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>分组树路径</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>54</v>
-      </c>
+      <c r="A13" s="0" t="n"/>
+      <c r="B13" s="0" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>责任科室空白</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>303</v>
-      </c>
+      <c r="A14" s="0" t="n"/>
+      <c r="B14" s="0" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>固定门诊根</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>全部终端&gt;门急诊&gt;门诊</t>
-        </is>
-      </c>
+      <c r="A15" s="0" t="n"/>
+      <c r="B15" s="0" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>固定急诊根</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>全部终端&gt;门急诊&gt;急诊</t>
-        </is>
-      </c>
+      <c r="A16" s="0" t="n"/>
+      <c r="B16" s="0" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
